--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/o-higgins.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/o-higgins.xlsx
@@ -745,7 +745,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +810,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +875,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1672,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1798,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1863,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2111,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2176,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2241,11 @@
           <t>76.399.126-1</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2306,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2493,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +2985,11 @@
           <t>77.798.686-4</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3294,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3359,11 @@
           <t>77.163.858-9</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3424,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3489,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3554,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3619,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3745,11 @@
           <t>77.362.622-7</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +3871,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +3997,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4062,11 @@
           <t>77.685.821-8</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4249,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4314,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4562,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4627,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4753,11 @@
           <t>77.601.843-0</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5123,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5249,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5314,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5379,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5505,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5570,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +5879,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +5944,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +6009,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6074,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6139,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6204,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6513,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6761,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +6948,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7211,7 +7379,11 @@
           <t>77.685.821-8</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7444,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7394,7 +7570,11 @@
           <t>77.362.622-7</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8184,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8187,7 +8371,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8436,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8370,7 +8562,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8431,7 +8627,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8736,7 +8936,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8797,7 +9001,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8919,7 +9127,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9041,7 +9253,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9285,7 +9501,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9346,7 +9566,11 @@
           <t>77.362.622-7</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9468,7 +9692,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9529,7 +9757,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9590,7 +9822,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9651,7 +9887,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9712,7 +9952,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9956,7 +10200,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10139,7 +10387,11 @@
           <t>77.795.374-5</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10200,7 +10452,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10322,7 +10578,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10444,7 +10704,11 @@
           <t>77.362.622-7</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10505,7 +10769,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10566,7 +10834,11 @@
           <t>77.362.622-7</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10627,7 +10899,11 @@
           <t>77.610.398-5</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10688,7 +10964,11 @@
           <t>77.610.398-5</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10810,7 +11090,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10871,7 +11155,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10932,7 +11220,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10993,7 +11285,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11054,7 +11350,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11115,7 +11415,11 @@
           <t>77.610.398-5</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11176,7 +11480,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11359,7 +11667,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11603,7 +11915,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11908,7 +12224,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12091,7 +12411,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12335,7 +12659,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12457,7 +12785,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12518,7 +12850,11 @@
           <t>77.610.398-5</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12640,7 +12976,11 @@
           <t>84.634.200-1</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12762,7 +13102,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12823,7 +13167,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12884,7 +13232,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13189,7 +13541,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13372,7 +13728,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13433,7 +13793,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13494,7 +13858,11 @@
           <t>77.685.821-8</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13555,7 +13923,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13616,7 +13988,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13738,7 +14114,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13799,7 +14179,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13860,7 +14244,11 @@
           <t>77.714.558-4</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14226,7 +14614,11 @@
           <t>77.685.821-8</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14287,7 +14679,11 @@
           <t>77.823.479-3</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14348,7 +14744,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14409,7 +14809,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14470,7 +14874,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14653,7 +15061,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14958,7 +15370,11 @@
           <t>77.685.821-8</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15019,7 +15435,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15202,7 +15622,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15507,7 +15931,11 @@
           <t>77.529.681-K</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15568,7 +15996,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15690,7 +16122,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16178,7 +16614,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16239,7 +16679,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16300,7 +16744,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16727,7 +17175,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16910,7 +17362,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17093,7 +17549,11 @@
           <t>77.685.821-8</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17154,7 +17614,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17215,7 +17679,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17276,7 +17744,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17703,7 +18175,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18008,7 +18484,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18069,7 +18549,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18252,7 +18736,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18374,7 +18862,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18557,7 +19049,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/o-higgins.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/o-higgins.xlsx
@@ -1489,7 +1489,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7135,7 +7139,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/o-higgins.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/o-higgins.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M303"/>
+  <dimension ref="A1:M310"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2514,7 +2514,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2778-163-CM25</t>
+          <t>1213444-97-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2534,17 +2534,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>71.328.600-1</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>CORP MUNICIPAL SAN FERNANDO PARA LA ATENCION MENORES Y LAS A DE E Y S</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2554,12 +2554,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>76.962.756-1</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2569,13 +2569,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>1495.12</v>
+        <v>13988.76</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1213444-97-CM25</t>
+          <t>2778-163-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2595,17 +2595,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>71.328.600-1</t>
+          <t>69.081.200-2</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL SAN FERNANDO PARA LA ATENCION MENORES Y LAS A DE E Y S</t>
+          <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2615,12 +2615,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>13988.76</v>
+        <v>1495.12</v>
       </c>
     </row>
     <row r="36">
@@ -4457,7 +4457,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>3958-122-CM25</t>
+          <t>2401-357-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>69.073.800-7</t>
+          <t>69.080.100-0</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NAVIDAD</t>
+          <t>I MUNICIPALIDAD DE RANCAGUA</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4497,28 +4497,32 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TD TODO EXPRESS LIMITADA</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>76.967.556-6</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
+          <t>76.148.628-4</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>4303.63</v>
+        <v>8177.35</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2401-357-CM25</t>
+          <t>3958-123-CM25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4543,12 +4547,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>69.080.100-0</t>
+          <t>69.073.800-7</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RANCAGUA</t>
+          <t>I MUNICIPALIDAD DE NAVIDAD</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4558,12 +4562,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4577,13 +4581,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>8177.35</v>
+        <v>1004.74</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>3958-123-CM25</t>
+          <t>3958-122-CM25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4623,26 +4627,22 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>COMERCIALIZADORA TD TODO EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.967.556-6</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>1004.74</v>
+        <v>4303.63</v>
       </c>
     </row>
     <row r="68">
@@ -5461,7 +5461,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>3371-53-CM25</t>
+          <t>3928-375-CM25</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5486,12 +5486,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>61.946.700-0</t>
+          <t>69.091.201-5</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5501,26 +5501,22 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
+          <t>MAXVAL SPA</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>77.745.829-9</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.290.944-6</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>5329.84</v>
+        <v>1170.03</v>
       </c>
     </row>
     <row r="82">
@@ -5591,7 +5587,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>3928-375-CM25</t>
+          <t>3371-53-CM25</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5616,12 +5612,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>69.091.201-5</t>
+          <t>61.946.700-0</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5631,22 +5627,26 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>MAXVAL SPA</t>
+          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>77.290.944-6</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr"/>
+          <t>77.745.829-9</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>1170.03</v>
+        <v>5329.84</v>
       </c>
     </row>
     <row r="84">
@@ -6225,7 +6225,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>3810-1360-CM25</t>
+          <t>3810-1358-CM25</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6280,13 +6280,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>991.79</v>
+        <v>2624.14</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>3810-1358-CM25</t>
+          <t>3810-1360-CM25</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6341,7 +6341,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>2624.14</v>
+        <v>991.79</v>
       </c>
     </row>
     <row r="95">
@@ -6843,7 +6843,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1350767-87-CM25</t>
+          <t>3371-69-CM25</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6868,7 +6868,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>61.981.210-7</t>
+          <t>61.946.700-0</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -6883,28 +6883,32 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA LA MAULINA LTDA.</t>
+          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>76.099.725-0</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr"/>
+          <t>77.745.829-9</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>4390.45</v>
+        <v>723</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>3371-69-CM25</t>
+          <t>1350767-87-CM25</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6929,7 +6933,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>61.946.700-0</t>
+          <t>61.981.210-7</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -6944,26 +6948,22 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
+          <t>COMERCIALIZADORA LA MAULINA LTDA.</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>77.745.829-9</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.099.725-0</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>723</v>
+        <v>4390.45</v>
       </c>
     </row>
     <row r="105">
@@ -7278,7 +7278,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>3863-343-CM25</t>
+          <t>4562-243-CM25</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7298,17 +7298,17 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>69.090.600-7</t>
+          <t>69.080.300-3</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
+          <t>I MUNICIPALIDAD DE GRANEROS</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7318,28 +7318,32 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>PROYECTOS &amp; REMODELACIONES C&amp;O SPA</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr"/>
+          <t>77.685.821-8</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>4368.72</v>
+        <v>16248.32</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>4562-243-CM25</t>
+          <t>3863-343-CM25</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7359,17 +7363,17 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>69.080.300-3</t>
+          <t>69.090.600-7</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GRANEROS</t>
+          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7379,26 +7383,22 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>PROYECTOS &amp; REMODELACIONES C&amp;O SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>77.685.821-8</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>16248.32</v>
+        <v>4368.72</v>
       </c>
     </row>
     <row r="112">
@@ -7717,7 +7717,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2776-762-CM25</t>
+          <t>3810-1565-CM25</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>69.091.200-7</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL NOVA SEGURI DAD LIMITADA</t>
+          <t>MAXVAL SPA</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>78.610.360-6</t>
+          <t>77.290.944-6</t>
         </is>
       </c>
       <c r="K117" t="inlineStr"/>
@@ -7772,13 +7772,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>8055.76</v>
+        <v>1063.17</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>3810-1565-CM25</t>
+          <t>2776-762-CM25</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>69.091.200-7</t>
+          <t>69.081.200-2</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
+          <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7818,12 +7818,12 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>MAXVAL SPA</t>
+          <t>COMERCIAL E INDUSTRIAL NOVA SEGURI DAD LIMITADA</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>77.290.944-6</t>
+          <t>78.610.360-6</t>
         </is>
       </c>
       <c r="K118" t="inlineStr"/>
@@ -7833,7 +7833,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>1063.17</v>
+        <v>8055.76</v>
       </c>
     </row>
     <row r="119">
@@ -9087,7 +9087,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>4737-181-CM25</t>
+          <t>4374-133-CM25</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -9112,12 +9112,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>69.080.400-K</t>
+          <t>72.240.400-9</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CODEGUA</t>
+          <t>GOBIERNO REGIONAL VI REGION DEL LI BERTADOR B O"HIGGINS</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -9127,32 +9127,28 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>77.745.829-9</t>
-        </is>
-      </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.178.855-8</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>1125.76</v>
+        <v>3728.62</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>4374-133-CM25</t>
+          <t>4737-181-CM25</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -9177,12 +9173,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>72.240.400-9</t>
+          <t>69.080.400-K</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VI REGION DEL LI BERTADOR B O"HIGGINS</t>
+          <t>I MUNICIPALIDAD DE CODEGUA</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -9192,22 +9188,26 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
+          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>76.178.855-8</t>
-        </is>
-      </c>
-      <c r="K140" t="inlineStr"/>
+          <t>77.745.829-9</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>3728.62</v>
+        <v>1125.76</v>
       </c>
     </row>
     <row r="141">
@@ -11180,7 +11180,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>1137833-276-CM25</t>
+          <t>2568-2291-CM25</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11200,17 +11200,17 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>65.071.304-4</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>CORPORACION DE LA CULTURA Y LAS ARTES DE LA ILUSTRE MUNICIPALIDAD DE R</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -11220,17 +11220,17 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>COMERCIAL RENHET SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>77.619.564-2</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -11239,13 +11239,13 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>793.39</v>
+        <v>8488.85</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2568-2291-CM25</t>
+          <t>1137833-276-CM25</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -11265,17 +11265,17 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>65.071.304-4</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>CORPORACION DE LA CULTURA Y LAS ARTES DE LA ILUSTRE MUNICIPALIDAD DE R</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -11285,17 +11285,17 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIAL RENHET SPA</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.619.564-2</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -11304,7 +11304,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>8488.85</v>
+        <v>793.39</v>
       </c>
     </row>
     <row r="174">
@@ -11753,7 +11753,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>3663-65-CM26</t>
+          <t>1079563-20-CM26</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11773,17 +11773,17 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>69.081.300-9</t>
+          <t>61.978.680-7</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE REQUINOA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -11793,28 +11793,32 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>MAR DEL SUR SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>83.610.800-0</t>
-        </is>
-      </c>
-      <c r="K181" t="inlineStr"/>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>2879.16</v>
+        <v>9159.23</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>1079563-19-CM26</t>
+          <t>3663-65-CM26</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11834,17 +11838,17 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>61.978.680-7</t>
+          <t>69.081.300-9</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE REQUINOA</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -11854,12 +11858,12 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
+          <t>MAR DEL SUR SPA</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>76.178.855-8</t>
+          <t>83.610.800-0</t>
         </is>
       </c>
       <c r="K182" t="inlineStr"/>
@@ -11869,13 +11873,13 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>1778.17</v>
+        <v>2879.16</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>1079563-20-CM26</t>
+          <t>1079563-19-CM26</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11915,26 +11919,22 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
-        </is>
-      </c>
-      <c r="K183" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.178.855-8</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr"/>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>9159.23</v>
+        <v>1778.17</v>
       </c>
     </row>
     <row r="184">
@@ -12184,7 +12184,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>3946-63-CM26</t>
+          <t>3810-129-CM26</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -12204,17 +12204,17 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>69.081.100-6</t>
+          <t>69.091.200-7</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICHIDEGUA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -12224,32 +12224,28 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>MAXVAL SPA</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
-        </is>
-      </c>
-      <c r="K188" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.290.944-6</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr"/>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>2655.93</v>
+        <v>823.74</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>3810-129-CM26</t>
+          <t>3946-63-CM26</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -12269,17 +12265,17 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>69.091.200-7</t>
+          <t>69.081.100-6</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
+          <t>I MUNICIPALIDAD DE PICHIDEGUA</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -12289,22 +12285,26 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>MAXVAL SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>77.290.944-6</t>
-        </is>
-      </c>
-      <c r="K189" t="inlineStr"/>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>823.74</v>
+        <v>2655.93</v>
       </c>
     </row>
     <row r="190">
@@ -13257,7 +13257,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2776-124-CM26</t>
+          <t>1213444-88-CM26</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -13277,17 +13277,17 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>71.328.600-1</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>CORP MUNICIPAL SAN FERNANDO PARA LA ATENCION MENORES Y LAS A DE E Y S</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -13297,12 +13297,12 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K205" t="inlineStr"/>
@@ -13312,13 +13312,13 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>2549.2</v>
+        <v>1270.18</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>1213444-88-CM26</t>
+          <t>2776-124-CM26</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -13338,17 +13338,17 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>71.328.600-1</t>
+          <t>69.081.200-2</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL SAN FERNANDO PARA LA ATENCION MENORES Y LAS A DE E Y S</t>
+          <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -13358,12 +13358,12 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K206" t="inlineStr"/>
@@ -13373,13 +13373,13 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>1270.18</v>
+        <v>2549.2</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2776-140-CM26</t>
+          <t>4737-18-CM26</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13404,12 +13404,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>69.080.400-K</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>I MUNICIPALIDAD DE CODEGUA</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -13419,22 +13419,26 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>SOSEG SPA</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>76.897.534-5</t>
-        </is>
-      </c>
-      <c r="K207" t="inlineStr"/>
+          <t>76.148.628-4</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>1095.56</v>
+        <v>961.5</v>
       </c>
     </row>
     <row r="208">
@@ -13501,7 +13505,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>4737-18-CM26</t>
+          <t>2776-140-CM26</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13526,12 +13530,12 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>69.080.400-K</t>
+          <t>69.081.200-2</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CODEGUA</t>
+          <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -13541,26 +13545,22 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>SOSEG SPA</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
-        </is>
-      </c>
-      <c r="K209" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.897.534-5</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr"/>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>961.5</v>
+        <v>1095.56</v>
       </c>
     </row>
     <row r="210">
@@ -13627,7 +13627,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>1079563-71-CM26</t>
+          <t>3946-132-CM26</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -13647,17 +13647,17 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>61.978.680-7</t>
+          <t>69.081.100-6</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE PICHIDEGUA</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -13667,28 +13667,32 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>Francisco javier</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>76.882.403-7</t>
-        </is>
-      </c>
-      <c r="K211" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>818.54</v>
+        <v>23588.32</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>3946-132-CM26</t>
+          <t>1079563-71-CM26</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -13708,17 +13712,17 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>69.081.100-6</t>
+          <t>61.978.680-7</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICHIDEGUA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -13728,32 +13732,28 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>Francisco javier</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K212" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>76.882.403-7</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr"/>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>23588.32</v>
+        <v>818.54</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>1350767-30-CM26</t>
+          <t>4737-21-CM26</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -13778,12 +13778,12 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>61.981.210-7</t>
+          <t>69.080.400-K</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE CODEGUA</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -13793,12 +13793,12 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
+          <t>PROYECTOS &amp; REMODELACIONES C&amp;O SPA</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>77.745.829-9</t>
+          <t>77.685.821-8</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
@@ -13812,13 +13812,13 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>3229.31</v>
+        <v>2166.61</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>4737-21-CM26</t>
+          <t>1350767-30-CM26</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -13843,12 +13843,12 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>69.080.400-K</t>
+          <t>61.981.210-7</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CODEGUA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -13858,12 +13858,12 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>PROYECTOS &amp; REMODELACIONES C&amp;O SPA</t>
+          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>77.685.821-8</t>
+          <t>77.745.829-9</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
@@ -13877,7 +13877,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>2166.61</v>
+        <v>3229.31</v>
       </c>
     </row>
     <row r="215">
@@ -14013,7 +14013,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2776-200-CM26</t>
+          <t>1627-439-CM26</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -14033,17 +14033,17 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>61.602.145-1</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN FERNANDO</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -14053,28 +14053,32 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>SOSEG SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>76.897.534-5</t>
-        </is>
-      </c>
-      <c r="K217" t="inlineStr"/>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>1222.04</v>
+        <v>7940.35</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>1627-439-CM26</t>
+          <t>1627-440-CM26</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -14094,7 +14098,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -14114,17 +14118,17 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
@@ -14133,13 +14137,13 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>7940.35</v>
+        <v>16345.08</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>1627-440-CM26</t>
+          <t>2776-200-CM26</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -14164,12 +14168,12 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>61.602.145-1</t>
+          <t>69.081.200-2</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN FERNANDO</t>
+          <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -14179,26 +14183,22 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>SOSEG SPA</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K219" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>76.897.534-5</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr"/>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>16345.08</v>
+        <v>1222.04</v>
       </c>
     </row>
     <row r="220">
@@ -14391,7 +14391,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2778-159-CM26</t>
+          <t>4737-48-CM26</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -14416,12 +14416,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>69.080.400-K</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>I MUNICIPALIDAD DE CODEGUA</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -14431,28 +14431,32 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>EASY RETAIL S.A. .-</t>
+          <t>PROYECTOS &amp; REMODELACIONES C&amp;O SPA</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>76.568.660-1</t>
-        </is>
-      </c>
-      <c r="K223" t="inlineStr"/>
+          <t>77.685.821-8</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>1019.8</v>
+        <v>5361.55</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2778-160-CM26</t>
+          <t>2778-159-CM26</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -14492,12 +14496,12 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>EASY RETAIL S.A. .-</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>76.568.660-1</t>
         </is>
       </c>
       <c r="K224" t="inlineStr"/>
@@ -14507,13 +14511,13 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>1852.11</v>
+        <v>1019.8</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>4590-6-CM26</t>
+          <t>2778-160-CM26</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -14533,17 +14537,17 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.081.200-2</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -14553,12 +14557,12 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K225" t="inlineStr"/>
@@ -14568,13 +14572,13 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>22557.67</v>
+        <v>1852.11</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>4737-48-CM26</t>
+          <t>4590-6-CM26</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -14594,17 +14598,17 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>69.080.400-K</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CODEGUA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -14614,32 +14618,28 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>PROYECTOS &amp; REMODELACIONES C&amp;O SPA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>77.685.821-8</t>
-        </is>
-      </c>
-      <c r="K226" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.961.103-7</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr"/>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>5361.55</v>
+        <v>22557.67</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>1622-531-CM26</t>
+          <t>2778-211-CM26</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -14659,17 +14659,17 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>61.602.141-9</t>
+          <t>69.081.200-2</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
+          <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -14679,17 +14679,17 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>COMERCIAL TRANCURA SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>77.823.479-3</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
@@ -14698,13 +14698,13 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>793.86</v>
+        <v>6784.23</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2778-211-CM26</t>
+          <t>1622-531-CM26</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -14724,17 +14724,17 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>61.602.141-9</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -14744,17 +14744,17 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIAL TRANCURA SPA</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.823.479-3</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
@@ -14763,13 +14763,13 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>6784.23</v>
+        <v>793.86</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2778-232-CM26</t>
+          <t>4737-52-CM26</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>69.080.400-K</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>I MUNICIPALIDAD DE CODEGUA</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -14809,17 +14809,17 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIALIZADORA INFINITO SPA</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.499.324-K</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
@@ -14828,13 +14828,13 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>4656.81</v>
+        <v>1076.24</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>4737-52-CM26</t>
+          <t>2778-232-CM26</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -14859,12 +14859,12 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>69.080.400-K</t>
+          <t>69.081.200-2</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CODEGUA</t>
+          <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -14874,17 +14874,17 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA INFINITO SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>77.499.324-K</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
@@ -14893,13 +14893,13 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>1076.24</v>
+        <v>4656.81</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2776-270-CM26</t>
+          <t>3810-372-CM26</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -14924,12 +14924,12 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>69.091.200-7</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -14939,12 +14939,12 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>SOSEG SPA</t>
+          <t>MAXVAL SPA</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>76.897.534-5</t>
+          <t>77.290.944-6</t>
         </is>
       </c>
       <c r="K231" t="inlineStr"/>
@@ -14954,13 +14954,13 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>1249.2</v>
+        <v>1810.17</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>3810-372-CM26</t>
+          <t>2776-270-CM26</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -14985,12 +14985,12 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>69.091.200-7</t>
+          <t>69.081.200-2</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
+          <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -15000,12 +15000,12 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>MAXVAL SPA</t>
+          <t>SOSEG SPA</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>77.290.944-6</t>
+          <t>76.897.534-5</t>
         </is>
       </c>
       <c r="K232" t="inlineStr"/>
@@ -15015,7 +15015,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>1810.17</v>
+        <v>1249.2</v>
       </c>
     </row>
     <row r="233">
@@ -15208,7 +15208,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>3810-406-CM26</t>
+          <t>3634-197-CM26</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -15233,12 +15233,12 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>69.091.200-7</t>
+          <t>69.081.500-1</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
+          <t>I MUNICIPALIDAD DE MALLOA</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -15248,12 +15248,12 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>MAXVAL SPA</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>77.290.944-6</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K236" t="inlineStr"/>
@@ -15263,13 +15263,13 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>792.88</v>
+        <v>6195.51</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>3634-197-CM26</t>
+          <t>3810-406-CM26</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -15294,12 +15294,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>69.081.500-1</t>
+          <t>69.091.200-7</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MALLOA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -15309,12 +15309,12 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>MAXVAL SPA</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>77.290.944-6</t>
         </is>
       </c>
       <c r="K237" t="inlineStr"/>
@@ -15324,7 +15324,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>6195.51</v>
+        <v>792.88</v>
       </c>
     </row>
     <row r="238">
@@ -15582,7 +15582,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>3690-154-CM26</t>
+          <t>1529-151-CM26</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -15602,17 +15602,17 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>69.080.800-5</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAS CABRAS</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -15622,32 +15622,28 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>COMERCIAL E INDUSTRIAL NOVA SEGURI DAD LIMITADA</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
-        </is>
-      </c>
-      <c r="K242" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.610.360-6</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr"/>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>4934.67</v>
+        <v>1628.47</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>1529-151-CM26</t>
+          <t>3690-154-CM26</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -15667,17 +15663,17 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>69.080.800-5</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>I MUNICIPALIDAD DE LAS CABRAS</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -15687,22 +15683,26 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL NOVA SEGURI DAD LIMITADA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>78.610.360-6</t>
-        </is>
-      </c>
-      <c r="K243" t="inlineStr"/>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>1628.47</v>
+        <v>4934.67</v>
       </c>
     </row>
     <row r="244">
@@ -16269,7 +16269,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>4371-259-CM26</t>
+          <t>3810-630-CM26</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -16294,12 +16294,12 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>69.081.000-k</t>
+          <t>69.091.200-7</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN VICENTE</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -16309,12 +16309,12 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>MAXVAL SPA</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>77.290.944-6</t>
         </is>
       </c>
       <c r="K253" t="inlineStr"/>
@@ -16324,13 +16324,13 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>2760.5</v>
+        <v>5144.45</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>3810-630-CM26</t>
+          <t>4371-259-CM26</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -16355,12 +16355,12 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>69.091.200-7</t>
+          <t>69.081.000-k</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
+          <t>I MUNICIPALIDAD DE SAN VICENTE</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -16370,12 +16370,12 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>MAXVAL SPA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>77.290.944-6</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K254" t="inlineStr"/>
@@ -16385,7 +16385,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>5144.45</v>
+        <v>2760.5</v>
       </c>
     </row>
     <row r="255">
@@ -16513,7 +16513,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>2776-439-CM26</t>
+          <t>2776-440-CM26</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -16533,7 +16533,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -16553,28 +16553,32 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
-        </is>
-      </c>
-      <c r="K257" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>842.8200000000001</v>
+        <v>1758.87</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>2776-440-CM26</t>
+          <t>2776-439-CM26</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -16594,7 +16598,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -16614,32 +16618,28 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K258" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>76.231.391-K</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr"/>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>1758.87</v>
+        <v>842.8200000000001</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>2776-445-CM26</t>
+          <t>3730-428-CM26</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -16664,12 +16664,12 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>69.090.300-8</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>I MUNICIPALIDAD DE CHIMBARONGO</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -16679,26 +16679,22 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIAL COMPARO LIMITADA</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K259" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>76.290.943-K</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr"/>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>1009.31</v>
+        <v>2521.08</v>
       </c>
     </row>
     <row r="260">
@@ -16769,7 +16765,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>3730-428-CM26</t>
+          <t>2776-445-CM26</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -16794,12 +16790,12 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>69.090.300-8</t>
+          <t>69.081.200-2</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHIMBARONGO</t>
+          <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -16809,22 +16805,26 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>COMERCIAL COMPARO LIMITADA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>76.290.943-K</t>
-        </is>
-      </c>
-      <c r="K261" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>2521.08</v>
+        <v>1009.31</v>
       </c>
     </row>
     <row r="262">
@@ -16952,7 +16952,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>745-29-CM26</t>
+          <t>594965-111-CM26</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -16977,12 +16977,12 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -16992,12 +16992,12 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>Energía del Futuro</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>76.577.971-5</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K264" t="inlineStr"/>
@@ -17007,13 +17007,13 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>5265.24</v>
+        <v>8402.219999999999</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>594965-111-CM26</t>
+          <t>745-29-CM26</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -17038,12 +17038,12 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -17053,12 +17053,12 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>Energía del Futuro</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.577.971-5</t>
         </is>
       </c>
       <c r="K265" t="inlineStr"/>
@@ -17068,7 +17068,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>8402.219999999999</v>
+        <v>5265.24</v>
       </c>
     </row>
     <row r="266">
@@ -17135,7 +17135,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>4591-24-CM26</t>
+          <t>3810-745-CM26</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -17160,12 +17160,12 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.091.200-7</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -17175,32 +17175,28 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>MAXVAL SPA</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K267" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>77.290.944-6</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr"/>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>23259.68</v>
+        <v>8691.200000000001</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>3810-745-CM26</t>
+          <t>4591-24-CM26</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -17225,12 +17221,12 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>69.091.200-7</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -17240,22 +17236,26 @@
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>MAXVAL SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>77.290.944-6</t>
-        </is>
-      </c>
-      <c r="K268" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>8691.200000000001</v>
+        <v>23259.68</v>
       </c>
     </row>
     <row r="269">
@@ -17769,7 +17769,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>3810-787-CM26</t>
+          <t>4371-344-CM26</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -17794,12 +17794,12 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>69.091.200-7</t>
+          <t>69.081.000-k</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
+          <t>I MUNICIPALIDAD DE SAN VICENTE</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -17809,12 +17809,12 @@
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>IMPORTADORA Y COMERCIALIZADORA DE SISTEMAS GENERADORES DE ENERGIA POWE</t>
         </is>
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>76.206.192-9</t>
         </is>
       </c>
       <c r="K277" t="inlineStr"/>
@@ -17824,13 +17824,13 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>8755.809999999999</v>
+        <v>6607.38</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>4371-344-CM26</t>
+          <t>3810-787-CM26</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -17855,12 +17855,12 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>69.081.000-k</t>
+          <t>69.091.200-7</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN VICENTE</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -17870,12 +17870,12 @@
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y COMERCIALIZADORA DE SISTEMAS GENERADORES DE ENERGIA POWE</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>76.206.192-9</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K278" t="inlineStr"/>
@@ -17885,7 +17885,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>6607.38</v>
+        <v>8755.809999999999</v>
       </c>
     </row>
     <row r="279">
@@ -18074,7 +18074,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>3959-116-CM26</t>
+          <t>1350767-139-CM26</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -18094,17 +18094,17 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>69.073.800-7</t>
+          <t>61.981.210-7</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NAVIDAD</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -18114,28 +18114,32 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
-        </is>
-      </c>
-      <c r="K282" t="inlineStr"/>
+          <t>77.745.829-9</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>1538.59</v>
+        <v>4976.89</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>1350767-139-CM26</t>
+          <t>3959-116-CM26</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -18155,17 +18159,17 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>61.981.210-7</t>
+          <t>69.073.800-7</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE NAVIDAD</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -18175,26 +18179,22 @@
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>77.745.829-9</t>
-        </is>
-      </c>
-      <c r="K283" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr"/>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>4976.89</v>
+        <v>1538.59</v>
       </c>
     </row>
     <row r="284">
@@ -18444,7 +18444,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>2675-399-CM26</t>
+          <t>2675-400-CM26</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -18484,12 +18484,12 @@
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K288" t="inlineStr">
@@ -18503,13 +18503,13 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>2489.01</v>
+        <v>4944.04</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>2675-400-CM26</t>
+          <t>2675-399-CM26</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -18549,12 +18549,12 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K289" t="inlineStr">
@@ -18568,13 +18568,13 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>4944.04</v>
+        <v>2489.01</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>3810-907-CM26</t>
+          <t>3810-893-CM26</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -18629,13 +18629,13 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>3665.45</v>
+        <v>1940.71</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>3810-893-CM26</t>
+          <t>3810-907-CM26</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -18690,13 +18690,13 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>1940.71</v>
+        <v>3665.45</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>3664-201-CM26</t>
+          <t>3810-916-CM26</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -18716,17 +18716,17 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>69.081.300-9</t>
+          <t>69.091.200-7</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE REQUINOA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -18736,32 +18736,28 @@
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>MAXVAL SPA</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
-        </is>
-      </c>
-      <c r="K292" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.290.944-6</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr"/>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>1293.62</v>
+        <v>1009.56</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>3810-916-CM26</t>
+          <t>3664-201-CM26</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -18781,17 +18777,17 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>69.091.200-7</t>
+          <t>69.081.300-9</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
+          <t>I MUNICIPALIDAD DE REQUINOA</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -18801,22 +18797,26 @@
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>MAXVAL SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>77.290.944-6</t>
-        </is>
-      </c>
-      <c r="K293" t="inlineStr"/>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>1009.56</v>
+        <v>1293.62</v>
       </c>
     </row>
     <row r="294">
@@ -19196,7 +19196,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>3810-959-CM26</t>
+          <t>3810-960-CM26</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -19251,13 +19251,13 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>2714.09</v>
+        <v>2638.35</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>3810-960-CM26</t>
+          <t>3810-959-CM26</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -19312,13 +19312,13 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>2638.35</v>
+        <v>2714.09</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>3810-976-CM26</t>
+          <t>1213444-435-CM26</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -19343,12 +19343,12 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>69.091.200-7</t>
+          <t>71.328.600-1</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
+          <t>CORP MUNICIPAL SAN FERNANDO PARA LA ATENCION MENORES Y LAS A DE E Y S</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -19358,22 +19358,26 @@
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>MAXVAL SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>77.290.944-6</t>
-        </is>
-      </c>
-      <c r="K302" t="inlineStr"/>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>6932.11</v>
+        <v>1384.4</v>
       </c>
     </row>
     <row r="303">
@@ -19399,7 +19403,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
@@ -19435,6 +19439,445 @@
       </c>
       <c r="M303" s="2" t="n">
         <v>3776.08</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>3810-976-CM26</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>69.091.200-7</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>MAXVAL SPA</t>
+        </is>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>77.290.944-6</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr"/>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M304" s="2" t="n">
+        <v>6932.11</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>1213444-470-CM26</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>71.328.600-1</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>CORP MUNICIPAL SAN FERNANDO PARA LA ATENCION MENORES Y LAS A DE E Y S</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>COMERCIAL GRAN VIA SPA</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M305" s="2" t="n">
+        <v>3438.59</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>3690-281-CM26</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>69.080.800-5</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LAS CABRAS</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M306" s="2" t="n">
+        <v>8707.200000000001</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2675-455-CM26</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>69.080.500-6</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M307" s="2" t="n">
+        <v>3385.87</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2080-10020-CM26</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>61.602.138-9</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>86.887.200-4</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr"/>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M308" s="2" t="n">
+        <v>963.33</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>3810-1059-CM26</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>69.091.200-7</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>MAXVAL SPA</t>
+        </is>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>77.290.944-6</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr"/>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M309" s="2" t="n">
+        <v>4136.5</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>3810-1056-CM26</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>69.091.200-7</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>MAXVAL SPA</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>77.290.944-6</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr"/>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M310" s="2" t="n">
+        <v>4907.02</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/o-higgins.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/o-higgins.xlsx
@@ -13277,7 +13277,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -14033,7 +14033,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -14789,7 +14789,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -16041,7 +16041,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -16598,7 +16598,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -16720,7 +16720,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -16972,7 +16972,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -17033,7 +17033,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/o-higgins.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/o-higgins.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M310"/>
+  <dimension ref="A1:M311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -10286,7 +10286,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>3634-554-CM25</t>
+          <t>1469101-3-CM25</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10311,12 +10311,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>69.081.500-1</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MALLOA</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10326,28 +10326,32 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>INVERSIONES CHILE LIMITADA</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
-        </is>
-      </c>
-      <c r="K158" t="inlineStr"/>
+          <t>77.795.374-5</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>9398.959999999999</v>
+        <v>101307.36</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>1469101-3-CM25</t>
+          <t>3634-554-CM25</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10372,12 +10376,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>69.081.500-1</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>I MUNICIPALIDAD DE MALLOA</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10387,26 +10391,22 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>INVERSIONES CHILE LIMITADA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>77.795.374-5</t>
-        </is>
-      </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t>O'Higgins</t>
-        </is>
-      </c>
+          <t>76.579.703-9</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>101307.36</v>
+        <v>9398.959999999999</v>
       </c>
     </row>
     <row r="160">
@@ -11115,7 +11115,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>1137833-275-CM25</t>
+          <t>1137833-276-CM25</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -11155,12 +11155,12 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>COMERCIAL RENHET SPA</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>77.619.564-2</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
@@ -11174,13 +11174,13 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>1249.34</v>
+        <v>793.39</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2568-2291-CM25</t>
+          <t>1137833-275-CM25</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11200,17 +11200,17 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>65.071.304-4</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>CORPORACION DE LA CULTURA Y LAS ARTES DE LA ILUSTRE MUNICIPALIDAD DE R</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -11220,17 +11220,17 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -11239,13 +11239,13 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>8488.85</v>
+        <v>1249.34</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>1137833-276-CM25</t>
+          <t>2568-2291-CM25</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -11265,17 +11265,17 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>65.071.304-4</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>CORPORACION DE LA CULTURA Y LAS ARTES DE LA ILUSTRE MUNICIPALIDAD DE R</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -11285,17 +11285,17 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>COMERCIAL RENHET SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>77.619.564-2</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -11304,7 +11304,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>793.39</v>
+        <v>8488.85</v>
       </c>
     </row>
     <row r="174">
@@ -12684,7 +12684,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>4590-1-CM26</t>
+          <t>2675-59-CM26</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12704,17 +12704,17 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.080.500-6</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -12724,28 +12724,32 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>sociedad comercial aguad hnos y cia ltda</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>76.341.992-4</t>
-        </is>
-      </c>
-      <c r="K196" t="inlineStr"/>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>1402.87</v>
+        <v>3979.51</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2675-59-CM26</t>
+          <t>4590-1-CM26</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12765,17 +12769,17 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>69.080.500-6</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -12785,26 +12789,22 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>sociedad comercial aguad hnos y cia ltda</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
-        </is>
-      </c>
-      <c r="K197" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.341.992-4</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr"/>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>3979.51</v>
+        <v>1402.87</v>
       </c>
     </row>
     <row r="198">
@@ -13062,7 +13062,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2817-137-CM26</t>
+          <t>1529-72-CM26</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -13082,17 +13082,17 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>69.090.100-5</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FERNANDO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -13102,12 +13102,12 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>TECNOQUIM SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>76.378.846-6</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
@@ -13121,13 +13121,13 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>1714.17</v>
+        <v>1555.12</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>1529-72-CM26</t>
+          <t>2817-137-CM26</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -13147,17 +13147,17 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>69.090.100-5</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>I MUNICIPALIDAD DE SAN FERNANDO</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -13167,12 +13167,12 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>TECNOQUIM SPA</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>76.378.846-6</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
@@ -13186,7 +13186,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>1555.12</v>
+        <v>1714.17</v>
       </c>
     </row>
     <row r="204">
@@ -13257,7 +13257,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>1213444-88-CM26</t>
+          <t>2776-124-CM26</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -13282,12 +13282,12 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>71.328.600-1</t>
+          <t>69.081.200-2</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL SAN FERNANDO PARA LA ATENCION MENORES Y LAS A DE E Y S</t>
+          <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -13297,12 +13297,12 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K205" t="inlineStr"/>
@@ -13312,13 +13312,13 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>1270.18</v>
+        <v>2549.2</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2776-124-CM26</t>
+          <t>1213444-88-CM26</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -13343,12 +13343,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>71.328.600-1</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>CORP MUNICIPAL SAN FERNANDO PARA LA ATENCION MENORES Y LAS A DE E Y S</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -13358,12 +13358,12 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K206" t="inlineStr"/>
@@ -13373,13 +13373,13 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>2549.2</v>
+        <v>1270.18</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>4737-18-CM26</t>
+          <t>2776-140-CM26</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13404,12 +13404,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>69.080.400-K</t>
+          <t>69.081.200-2</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CODEGUA</t>
+          <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -13419,26 +13419,22 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>SOSEG SPA</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
-        </is>
-      </c>
-      <c r="K207" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.897.534-5</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr"/>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>961.5</v>
+        <v>1095.56</v>
       </c>
     </row>
     <row r="208">
@@ -13505,7 +13501,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2776-140-CM26</t>
+          <t>4737-18-CM26</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13530,12 +13526,12 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>69.080.400-K</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>I MUNICIPALIDAD DE CODEGUA</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -13545,22 +13541,26 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>SOSEG SPA</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>76.897.534-5</t>
-        </is>
-      </c>
-      <c r="K209" t="inlineStr"/>
+          <t>76.148.628-4</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>1095.56</v>
+        <v>961.5</v>
       </c>
     </row>
     <row r="210">
@@ -14078,7 +14078,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>1627-440-CM26</t>
+          <t>2776-200-CM26</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -14103,12 +14103,12 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>61.602.145-1</t>
+          <t>69.081.200-2</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN FERNANDO</t>
+          <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -14118,32 +14118,28 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>SOSEG SPA</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K218" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>76.897.534-5</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr"/>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>16345.08</v>
+        <v>1222.04</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2776-200-CM26</t>
+          <t>1627-440-CM26</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -14168,12 +14164,12 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>61.602.145-1</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN FERNANDO</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -14183,22 +14179,26 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>SOSEG SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>76.897.534-5</t>
-        </is>
-      </c>
-      <c r="K219" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>1222.04</v>
+        <v>16345.08</v>
       </c>
     </row>
     <row r="220">
@@ -14391,7 +14391,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>4737-48-CM26</t>
+          <t>2778-159-CM26</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -14416,12 +14416,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>69.080.400-K</t>
+          <t>69.081.200-2</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CODEGUA</t>
+          <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -14431,32 +14431,28 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>PROYECTOS &amp; REMODELACIONES C&amp;O SPA</t>
+          <t>EASY RETAIL S.A. .-</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>77.685.821-8</t>
-        </is>
-      </c>
-      <c r="K223" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.568.660-1</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr"/>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>5361.55</v>
+        <v>1019.8</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2778-159-CM26</t>
+          <t>2778-160-CM26</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -14496,12 +14492,12 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>EASY RETAIL S.A. .-</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>76.568.660-1</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K224" t="inlineStr"/>
@@ -14511,13 +14507,13 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>1019.8</v>
+        <v>1852.11</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2778-160-CM26</t>
+          <t>4590-6-CM26</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -14537,17 +14533,17 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -14557,12 +14553,12 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>76.961.103-7</t>
         </is>
       </c>
       <c r="K225" t="inlineStr"/>
@@ -14572,13 +14568,13 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>1852.11</v>
+        <v>22557.67</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>4590-6-CM26</t>
+          <t>4737-48-CM26</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -14598,17 +14594,17 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.080.400-K</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE CODEGUA</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -14618,28 +14614,32 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>PROYECTOS &amp; REMODELACIONES C&amp;O SPA</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
-        </is>
-      </c>
-      <c r="K226" t="inlineStr"/>
+          <t>77.685.821-8</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>22557.67</v>
+        <v>5361.55</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2778-211-CM26</t>
+          <t>1622-531-CM26</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -14659,17 +14659,17 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>61.602.141-9</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -14679,17 +14679,17 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIAL TRANCURA SPA</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.823.479-3</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
@@ -14698,13 +14698,13 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>6784.23</v>
+        <v>793.86</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>1622-531-CM26</t>
+          <t>2778-211-CM26</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -14724,17 +14724,17 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>61.602.141-9</t>
+          <t>69.081.200-2</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
+          <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -14744,17 +14744,17 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>COMERCIAL TRANCURA SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>77.823.479-3</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
@@ -14763,7 +14763,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>793.86</v>
+        <v>6784.23</v>
       </c>
     </row>
     <row r="229">
@@ -15582,7 +15582,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>1529-151-CM26</t>
+          <t>3690-154-CM26</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -15602,17 +15602,17 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>69.080.800-5</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>I MUNICIPALIDAD DE LAS CABRAS</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -15622,28 +15622,32 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL NOVA SEGURI DAD LIMITADA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>78.610.360-6</t>
-        </is>
-      </c>
-      <c r="K242" t="inlineStr"/>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>1628.47</v>
+        <v>4934.67</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>3690-154-CM26</t>
+          <t>1529-151-CM26</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -15663,17 +15667,17 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>69.080.800-5</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAS CABRAS</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -15683,26 +15687,22 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>COMERCIAL E INDUSTRIAL NOVA SEGURI DAD LIMITADA</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
-        </is>
-      </c>
-      <c r="K243" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.610.360-6</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr"/>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>4934.67</v>
+        <v>1628.47</v>
       </c>
     </row>
     <row r="244">
@@ -16391,7 +16391,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>4371-260-CM26</t>
+          <t>3946-286-CM26</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -16411,17 +16411,17 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>69.081.000-k</t>
+          <t>69.081.100-6</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN VICENTE</t>
+          <t>I MUNICIPALIDAD DE PICHIDEGUA</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -16431,12 +16431,12 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y COMERCIALIZADORA DE SISTEMAS GENERADORES DE ENERGIA POWE</t>
+          <t>COMERCIAL CASTRO Y CASTRO LIMITADA</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>76.206.192-9</t>
+          <t>78.456.070-8</t>
         </is>
       </c>
       <c r="K255" t="inlineStr"/>
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>8073.52</v>
+        <v>2920.33</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>3946-286-CM26</t>
+          <t>4371-260-CM26</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -16472,17 +16472,17 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>69.081.100-6</t>
+          <t>69.081.000-k</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICHIDEGUA</t>
+          <t>I MUNICIPALIDAD DE SAN VICENTE</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -16492,12 +16492,12 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>COMERCIAL CASTRO Y CASTRO LIMITADA</t>
+          <t>IMPORTADORA Y COMERCIALIZADORA DE SISTEMAS GENERADORES DE ENERGIA POWE</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>78.456.070-8</t>
+          <t>76.206.192-9</t>
         </is>
       </c>
       <c r="K256" t="inlineStr"/>
@@ -16507,7 +16507,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>2920.33</v>
+        <v>8073.52</v>
       </c>
     </row>
     <row r="257">
@@ -16830,7 +16830,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>4591-20-CM26</t>
+          <t>3810-662-CM26</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -16855,12 +16855,12 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.091.200-7</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -16870,12 +16870,12 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>MAXVAL SPA</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>77.290.944-6</t>
         </is>
       </c>
       <c r="K262" t="inlineStr"/>
@@ -16885,13 +16885,13 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>2358.36</v>
+        <v>5166.48</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>3810-662-CM26</t>
+          <t>4591-20-CM26</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -16916,12 +16916,12 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>69.091.200-7</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -16931,12 +16931,12 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>MAXVAL SPA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>77.290.944-6</t>
+          <t>76.961.103-7</t>
         </is>
       </c>
       <c r="K263" t="inlineStr"/>
@@ -16946,7 +16946,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>5166.48</v>
+        <v>2358.36</v>
       </c>
     </row>
     <row r="264">
@@ -17135,7 +17135,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>3810-745-CM26</t>
+          <t>4591-24-CM26</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -17160,12 +17160,12 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>69.091.200-7</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -17175,28 +17175,32 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>MAXVAL SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>77.290.944-6</t>
-        </is>
-      </c>
-      <c r="K267" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>8691.200000000001</v>
+        <v>23259.68</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>4591-24-CM26</t>
+          <t>3810-745-CM26</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -17221,12 +17225,12 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.091.200-7</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -17236,32 +17240,28 @@
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>MAXVAL SPA</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K268" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>77.290.944-6</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr"/>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>23259.68</v>
+        <v>8691.200000000001</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>3810-764-CM26</t>
+          <t>2776-510-CM26</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -17281,17 +17281,17 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>69.091.200-7</t>
+          <t>69.081.200-2</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
+          <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -17301,28 +17301,32 @@
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>MAXVAL SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>77.290.944-6</t>
-        </is>
-      </c>
-      <c r="K269" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>5606.83</v>
+        <v>12569.86</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>2776-510-CM26</t>
+          <t>3810-766-CM26</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -17342,17 +17346,17 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>69.091.200-7</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -17362,32 +17366,28 @@
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>MAXVAL SPA</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K270" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>77.290.944-6</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr"/>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>12569.86</v>
+        <v>1047.89</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>3810-766-CM26</t>
+          <t>3810-764-CM26</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -17442,7 +17442,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>1047.89</v>
+        <v>5606.83</v>
       </c>
     </row>
     <row r="272">
@@ -17891,7 +17891,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>3810-788-CM26</t>
+          <t>3634-367-CM26</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -17916,12 +17916,12 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>69.091.200-7</t>
+          <t>69.081.500-1</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
+          <t>I MUNICIPALIDAD DE MALLOA</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -17931,12 +17931,12 @@
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>MAXVAL SPA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>77.290.944-6</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K279" t="inlineStr"/>
@@ -17946,7 +17946,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>5286.19</v>
+        <v>1692.67</v>
       </c>
     </row>
     <row r="280">
@@ -18013,7 +18013,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>3634-367-CM26</t>
+          <t>3810-788-CM26</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -18038,12 +18038,12 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>69.081.500-1</t>
+          <t>69.091.200-7</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MALLOA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -18053,12 +18053,12 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>MAXVAL SPA</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>77.290.944-6</t>
         </is>
       </c>
       <c r="K281" t="inlineStr"/>
@@ -18068,7 +18068,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>1692.67</v>
+        <v>5286.19</v>
       </c>
     </row>
     <row r="282">
@@ -18383,7 +18383,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>3810-878-CM26</t>
+          <t>2675-399-CM26</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -18408,12 +18408,12 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>69.091.200-7</t>
+          <t>69.080.500-6</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
+          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -18423,22 +18423,26 @@
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>MAXVAL SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>77.290.944-6</t>
-        </is>
-      </c>
-      <c r="K287" t="inlineStr"/>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>5201.62</v>
+        <v>2489.01</v>
       </c>
     </row>
     <row r="288">
@@ -18509,7 +18513,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>2675-399-CM26</t>
+          <t>3810-878-CM26</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -18534,12 +18538,12 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>69.080.500-6</t>
+          <t>69.091.200-7</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -18549,32 +18553,28 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>MAXVAL SPA</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
-        </is>
-      </c>
-      <c r="K289" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.290.944-6</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr"/>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>2489.01</v>
+        <v>5201.62</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>3810-893-CM26</t>
+          <t>3810-907-CM26</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -18629,13 +18629,13 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>1940.71</v>
+        <v>3665.45</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>3810-907-CM26</t>
+          <t>3810-893-CM26</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -18690,7 +18690,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>3665.45</v>
+        <v>1940.71</v>
       </c>
     </row>
     <row r="292">
@@ -19074,7 +19074,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>3810-952-CM26</t>
+          <t>3810-953-CM26</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -19094,7 +19094,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
@@ -19114,12 +19114,12 @@
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>MAXVAL SPA</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>77.290.944-6</t>
         </is>
       </c>
       <c r="K298" t="inlineStr"/>
@@ -19129,13 +19129,13 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>3961.65</v>
+        <v>1861.53</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>3810-953-CM26</t>
+          <t>3810-952-CM26</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -19155,7 +19155,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
@@ -19175,12 +19175,12 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>MAXVAL SPA</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>77.290.944-6</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K299" t="inlineStr"/>
@@ -19190,7 +19190,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>1861.53</v>
+        <v>3961.65</v>
       </c>
     </row>
     <row r="300">
@@ -19761,7 +19761,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>3810-1059-CM26</t>
+          <t>3810-1056-CM26</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -19781,7 +19781,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
@@ -19816,13 +19816,13 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>4136.5</v>
+        <v>4907.02</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>3810-1056-CM26</t>
+          <t>3810-1059-CM26</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -19842,7 +19842,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
@@ -19877,7 +19877,68 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>4907.02</v>
+        <v>4136.5</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>3016-596-CM26</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>69.090.500-0</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOLOL</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>COMERCIAL CASTRO Y CASTRO LIMITADA</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>78.456.070-8</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr"/>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M311" s="2" t="n">
+        <v>2906.97</v>
       </c>
     </row>
   </sheetData>
